--- a/shortreport.xlsx
+++ b/shortreport.xlsx
@@ -5,15 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kav's Downloads\UIPATHING\SalesOrderEntry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Documents\UiPath\UIpathSalesOrderEntry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817ABB04-187B-4667-AB84-D127A0EE1208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A51627-4216-42EC-9C1D-65F020952EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3225" yWindow="1590" windowWidth="21600" windowHeight="12960" xr2:uid="{72836020-03D0-4CDC-98C3-7D7E8EFA81FB}"/>
+    <workbookView minimized="1" xWindow="3732" yWindow="3732" windowWidth="17280" windowHeight="8880" xr2:uid="{72836020-03D0-4CDC-98C3-7D7E8EFA81FB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="6" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
     <t>CompanyName</t>
   </si>
@@ -87,6 +89,9 @@
   </si>
   <si>
     <t>Office Equipment Bundle: Wireless Mice, USB-C Cables, A4 Paper, Desk Lamps_x000D_</t>
+  </si>
+  <si>
+    <t>TotalAmount</t>
   </si>
 </sst>
 </file>
@@ -140,6 +145,197 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TotalAmount</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$2:$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Tech Horizon Distributors</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Summit Office Supplies</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Northwind Traders Ltd</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$2:$B$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2221.8000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1021.89</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>669.01</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9883-43C0-BD93-9D50B6AC4B6E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="238024671"/>
+        <c:axId val="238588111"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="238024671"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="238588111"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="238588111"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="238024671"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>71120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43C4005C-19C1-123E-2624-66EE494F6CC5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -458,11 +654,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56FBB2EE-8582-45DF-815F-8A416E6980AB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2D8A062-0B4C-4F71-BE12-E024F5831E31}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>2221.8000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>1021.89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>669.01</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA1BF85B-D33F-42DC-8A78-974BDBE4C359}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -482,7 +730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -502,7 +750,7 @@
         <v>2221.8000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -522,7 +770,7 @@
         <v>1021.89</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
